--- a/files/九龙-旺角-逸里1号.xlsx
+++ b/files/九龙-旺角-逸里1号.xlsx
@@ -17,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="18">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +119,11 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -188,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,6 +207,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,6 +255,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -627,7 +640,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1156,7 +1169,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1164,34 +1177,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H9" s="5" t="n">
+        <v>6244000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>22380</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5869360</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>21037</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1996,7 +2001,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2004,34 +2009,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H21" s="5" t="n">
+        <v>6125000</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>21953</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>5757500</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>20636</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -2836,7 +2833,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2844,34 +2841,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>6023000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>21588</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>5661620</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>20293</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2906,7 +2895,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2914,34 +2903,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H34" s="5" t="n">
+        <v>6294000</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>23055</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>5916360</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>21672</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3256,7 +3237,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3264,34 +3245,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H39" s="5" t="n">
+        <v>5972000</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>21405</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5613680</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>20121</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -3326,7 +3299,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3334,34 +3307,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>6258000</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>22923</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>5882520</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>21548</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -3396,7 +3361,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3404,34 +3369,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H41" s="5" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>23607</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>8366000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>22191</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -3536,7 +3493,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3544,34 +3501,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H43" s="5" t="n">
+        <v>8714000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>24273</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>8191160</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>22817</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3606,7 +3555,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3614,34 +3563,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H44" s="5" t="n">
+        <v>9509000</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>24196</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>8938460</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>22744</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3676,7 +3617,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3684,34 +3625,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H45" s="5" t="n">
+        <v>5921000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>21222</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>5565740</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>19949</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -3746,7 +3679,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3754,34 +3687,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H46" s="5" t="n">
+        <v>6222000</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>22791</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>5848680</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>21424</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -3816,7 +3741,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3824,34 +3749,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H47" s="5" t="n">
+        <v>8773000</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>23271</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>8246620</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>21874</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3956,7 +3873,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3964,34 +3881,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>8612000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>23989</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>8095280</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>22550</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -4026,7 +3935,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -4034,34 +3943,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H50" s="5" t="n">
+        <v>9398000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>23913</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>8834120</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>22479</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -4516,7 +4417,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4524,34 +4425,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H57" s="5" t="n">
+        <v>5819000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>20857</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>5469860</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>19605</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -4586,7 +4479,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4594,34 +4487,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H58" s="5" t="n">
+        <v>6149000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>22524</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>5780060</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>21172</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -4656,7 +4541,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4664,34 +4549,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H59" s="5" t="n">
+        <v>8594000</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>22796</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>8078360</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>21428</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -4796,7 +4673,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4804,34 +4681,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H61" s="5" t="n">
+        <v>8433000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>23490</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>7927020</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>22081</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4866,7 +4735,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4874,34 +4743,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H62" s="5" t="n">
+        <v>9232000</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>23491</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>8678080</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>22082</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -5356,7 +5217,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5364,34 +5225,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H69" s="5" t="n">
+        <v>5733000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>20548</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5389020</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>19315</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -5426,7 +5279,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5434,34 +5287,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H70" s="5" t="n">
+        <v>6077000</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>22260</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>5712380</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>20924</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5636,7 +5481,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5644,34 +5489,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>8178000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>22780</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>7687320</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>21413</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -5706,7 +5543,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5714,34 +5551,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>9011000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>22929</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>8470340</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>21553</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5776,7 +5605,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5784,34 +5613,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>5699000</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>20427</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>5357060</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>19201</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -5846,7 +5667,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5854,34 +5675,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H76" s="5" t="n">
+        <v>6005000</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>21996</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5644700</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>20677</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -5916,7 +5729,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5924,34 +5737,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H77" s="5" t="n">
+        <v>8390000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>22255</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>7886600</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>20919</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -6196,7 +6001,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6204,34 +6009,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H81" s="5" t="n">
+        <v>5665000</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>20305</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>5325100</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>19086</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -6266,7 +6063,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -6274,34 +6071,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H82" s="5" t="n">
+        <v>5932000</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>21729</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>5576080</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>20425</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -6336,7 +6125,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6344,34 +6133,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H83" s="5" t="n">
+        <v>8313000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>22050</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>7814220</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>20727</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -6476,7 +6257,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6484,34 +6265,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H85" s="5" t="n">
+        <v>7846000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>21855</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>7375240</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>20544</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -6546,7 +6319,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6554,34 +6327,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H86" s="5" t="n">
+        <v>8679000</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>22084</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>8158260</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>20759</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -7456,7 +7221,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7464,34 +7229,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H99" s="5" t="n">
+        <v>5512000</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>19756</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>5181280</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>18571</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
@@ -7526,7 +7283,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7534,34 +7291,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H100" s="5" t="n">
+        <v>5788000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>21201</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>5440720</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>19929</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -7596,7 +7345,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7604,34 +7353,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>7956000</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>21103</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7478640</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>19837</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7736,7 +7477,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7744,34 +7485,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H103" s="5" t="n">
+        <v>7387000</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>20577</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>6943780</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>19342</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
@@ -7806,7 +7539,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7814,34 +7547,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H104" s="5" t="n">
+        <v>8264000</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>21028</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>7768160</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>19766</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -7876,7 +7601,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7884,34 +7609,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H105" s="5" t="n">
+        <v>5461000</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>19573</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>5133340</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>18399</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -7946,7 +7663,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7954,34 +7671,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H106" s="5" t="n">
+        <v>5733000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>21000</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5389020</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>19740</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -8016,7 +7725,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -8024,34 +7733,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H107" s="5" t="n">
+        <v>7828000</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>20764</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>7358320</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>19518</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -8156,7 +7857,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -8164,34 +7865,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H109" s="5" t="n">
+        <v>7233000</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>20148</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>6799020</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>18939</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N109" s="3" t="inlineStr">
@@ -8296,7 +7989,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8304,34 +7997,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H111" s="5" t="n">
+        <v>5393000</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>19330</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>5069420</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>18170</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -8366,7 +8051,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8374,34 +8059,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H112" s="5" t="n">
+        <v>5679000</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>20802</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>5338260</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>19554</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -8436,7 +8113,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8444,34 +8121,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>7675000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>20358</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7214500</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>19137</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -8576,7 +8245,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -8584,34 +8253,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H115" s="5" t="n">
+        <v>7106000</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>19794</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>6679640</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>18606</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
@@ -8646,7 +8307,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -8654,34 +8315,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H116" s="5" t="n">
+        <v>7960000</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>20254</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>7482400</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>19039</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
@@ -8716,7 +8369,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -8724,34 +8377,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H117" s="5" t="n">
+        <v>5339000</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>19136</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>5018660</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>17988</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -8786,7 +8431,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -8794,34 +8439,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H118" s="5" t="n">
+        <v>5625000</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>20604</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>5287500</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>19368</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -8856,7 +8493,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8864,34 +8501,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H119" s="5" t="n">
+        <v>7522000</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>19952</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>7070680</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>18755</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N119" s="3" t="inlineStr">
@@ -8996,7 +8625,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -9004,34 +8633,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H121" s="5" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>19499</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>6580000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>18329</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr">
@@ -9066,7 +8687,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -9074,34 +8695,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H122" s="5" t="n">
+        <v>7794000</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>19832</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>7326360</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>18642</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天現金付款計劃</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -9558,120 +9171,120 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>逸里1号 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>126</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>126</t>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
 -
@@ -9679,7 +9292,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 358呎 (2房)
 -
@@ -9687,7 +9300,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -9695,7 +9308,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
 -
@@ -9703,7 +9316,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
 -
@@ -9711,7 +9324,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
 -
@@ -9721,12 +9334,12 @@
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
 -
@@ -9734,7 +9347,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 358呎 (2房)
 -
@@ -9742,7 +9355,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -9750,7 +9363,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
 -
@@ -9758,7 +9371,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
 -
@@ -9766,22 +9379,77 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
+$624万
+$22,380/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 358呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
 -
@@ -9789,7 +9457,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 358呎 (2房)
 -
@@ -9797,7 +9465,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -9805,7 +9473,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
 -
@@ -9813,7 +9481,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
 -
@@ -9821,22 +9489,77 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
+$612万
+$21,953/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 358呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
 -
@@ -9844,15 +9567,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 358呎 (2房)
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -9860,7 +9583,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
 -
@@ -9868,30 +9591,140 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
+$629万
+$23,055/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$602万
+$21,588/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+$951万
+$24,196/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$871万
+$24,273/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+$890万
+$23,607/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$626万
+$22,923/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
+$597万
+$21,405/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+$940万
+$23,913/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$861万
+$23,989/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+$877万
+$23,271/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$622万
+$22,791/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$592万
+$21,222/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
 -
@@ -9899,15 +9732,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 358呎 (2房)
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -9915,7 +9748,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
 -
@@ -9923,7 +9756,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
 -
@@ -9931,7 +9764,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
 -
@@ -9940,21 +9773,76 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
+$923万
+$23,491/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$843万
+$23,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+$859万
+$22,796/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$615万
+$22,524/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$582万
+$20,857/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 359呎 (2房)
 -
@@ -9962,7 +9850,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -9970,7 +9858,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
 -
@@ -9978,7 +9866,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
 -
@@ -9986,7 +9874,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
 -
@@ -9995,21 +9883,76 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
+$901万
+$22,929/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$818万
+$22,780/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$608万
+$22,260/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$573万
+$20,548/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 359呎 (2房)
 -
@@ -10017,7 +9960,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -10025,23 +9968,133 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
+$839万
+$22,255/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$600万
+$21,996/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$570万
+$20,427/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+$868万
+$22,084/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$785万
+$21,855/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+$831万
+$22,050/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
+$593万
+$21,729/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$566万
+$20,305/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
 -
@@ -10050,13 +10103,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
 -
@@ -10064,7 +10117,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 359呎 (2房)
 -
@@ -10072,7 +10125,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -10080,7 +10133,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
 -
@@ -10088,7 +10141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
 -
@@ -10096,7 +10149,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 279呎 (1房)
 -
@@ -10105,29 +10158,139 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 393呎 (2房)
+$826万
+$21,028/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$739万
+$20,577/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+$796万
+$21,103/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$579万
+$21,201/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$551万
+$19,756/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 359呎 (2房)
+$723万
+$20,148/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+$783万
+$20,764/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$573万
+$21,000/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$546万
+$19,573/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+$796万
+$20,254/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$711万
+$19,794/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 370呎 (2房)
 -
@@ -10135,683 +10298,133 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 377呎 (2房)
+$768万
+$20,358/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 273呎 (1房)
+$568万
+$20,802/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$539万
+$19,330/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 393呎 (2房)
+$779万
+$19,832/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (2房)
+$700万
+$19,499/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 370呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 377呎 (2房)
+$752万
+$19,952/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 273呎 (1房)
+$562万
+$20,604/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 279呎 (1房)
+$534万
+$19,136/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 355呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 321呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 333呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 340呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 236呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 359呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 370呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 377呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>E | 273呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 279呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 355呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 321呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 333呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 236呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 243呎 (1房)
 -
